--- a/nano-splits/v2.0.0/nano-splits-v2.0.0.xlsx
+++ b/nano-splits/v2.0.0/nano-splits-v2.0.0.xlsx
@@ -32,10 +32,10 @@
     </comment>
     <comment ref="B1" authorId="1">
       <text>
-        <t>A locally assigned identifier provided by the data provider for the dataset. It
-is used to reference an external metadata record that may be maintained
-independently, enabling traceability and supporting provenance tracking.
-Example: Visium_9OLC_A4_S1</t>
+        <t>An identifier assigned by the data provider to reference an external metadata
+record for the dataset. The external record may be maintained independently and
+can support dataset traceability and provenance tracking. Leave this field empty
+if no such identifier exists.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="1">
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="136">
   <si>
     <t>parent_sample_id</t>
   </si>
@@ -97,304 +97,364 @@
     <t>dataset_type</t>
   </si>
   <si>
+    <t>Cell DIVE</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000159</t>
+  </si>
+  <si>
+    <t>CODEX</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000160</t>
+  </si>
+  <si>
+    <t>Light Sheet</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000168</t>
+  </si>
+  <si>
+    <t>MIBI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000172</t>
+  </si>
+  <si>
+    <t>LC-MS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000194</t>
+  </si>
+  <si>
     <t>HiFi-Slide</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000195</t>
   </si>
   <si>
+    <t>Histology</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000197</t>
+  </si>
+  <si>
+    <t>PhenoCycler</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000199</t>
+  </si>
+  <si>
+    <t>CyCIF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000200</t>
+  </si>
+  <si>
+    <t>MALDI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000201</t>
+  </si>
+  <si>
+    <t>SIMS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000202</t>
+  </si>
+  <si>
+    <t>DESI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000204</t>
+  </si>
+  <si>
+    <t>Auto-fluorescence</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000205</t>
+  </si>
+  <si>
+    <t>Confocal</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000206</t>
+  </si>
+  <si>
+    <t>Thick section Multiphoton MxIF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000207</t>
+  </si>
+  <si>
+    <t>Second Harmonic Generation (SHG)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000208</t>
+  </si>
+  <si>
+    <t>Enhanced Stimulated Raman Spectroscopy (SRS)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
+  </si>
+  <si>
+    <t>10X Multiome</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000215</t>
+  </si>
+  <si>
+    <t>Molecular Cartography</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000217</t>
+  </si>
+  <si>
+    <t>CosMx Transcriptomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000218</t>
+  </si>
+  <si>
+    <t>Xenium</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
+  </si>
+  <si>
+    <t>MERFISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000221</t>
+  </si>
+  <si>
     <t>SNARE-seq2</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000264</t>
   </si>
   <si>
+    <t>2D Imaging Mass Cytometry</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000296</t>
+  </si>
+  <si>
+    <t>GeoMx (NGS)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000300</t>
+  </si>
+  <si>
+    <t>GeoMx (nCounter)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000301</t>
+  </si>
+  <si>
+    <t>Visium (no probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000302</t>
+  </si>
+  <si>
+    <t>Visium (with probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000303</t>
+  </si>
+  <si>
+    <t>ATACseq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000309</t>
+  </si>
+  <si>
+    <t>RNAseq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000310</t>
+  </si>
+  <si>
+    <t>RNAseq (with probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
+  </si>
+  <si>
+    <t>nanoSPLITS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000312</t>
+  </si>
+  <si>
+    <t>MUSIC</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000328</t>
+  </si>
+  <si>
+    <t>Resolve</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000384</t>
+  </si>
+  <si>
+    <t>Stereo-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000385</t>
+  </si>
+  <si>
+    <t>Seq-Scope</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000390</t>
+  </si>
+  <si>
+    <t>DART-FISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000396</t>
+  </si>
+  <si>
+    <t>seqFISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000397</t>
+  </si>
+  <si>
+    <t>MS Lipidomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000405</t>
+  </si>
+  <si>
+    <t>CyTOF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000407</t>
+  </si>
+  <si>
+    <t>DBiT-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000428</t>
+  </si>
+  <si>
+    <t>Singular Genomics G4X</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000429</t>
+  </si>
+  <si>
+    <t>CosMx Proteomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000435</t>
+  </si>
+  <si>
+    <t>FACS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000440</t>
+  </si>
+  <si>
+    <t>Olink</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000441</t>
+  </si>
+  <si>
+    <t>4i</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000447</t>
+  </si>
+  <si>
+    <t>MPLEx</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000448</t>
+  </si>
+  <si>
+    <t>Pixel-seqV2</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000450</t>
+  </si>
+  <si>
+    <t>Visium HD</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000451</t>
+  </si>
+  <si>
     <t>COMET</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000458</t>
   </si>
   <si>
-    <t>Visium (no probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000302</t>
-  </si>
-  <si>
-    <t>DESI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000204</t>
-  </si>
-  <si>
-    <t>Confocal</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000206</t>
-  </si>
-  <si>
-    <t>Stereo-seq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000385</t>
-  </si>
-  <si>
-    <t>Visium (with probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000303</t>
-  </si>
-  <si>
-    <t>Molecular Cartography</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000217</t>
-  </si>
-  <si>
-    <t>DBiT-seq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000428</t>
-  </si>
-  <si>
-    <t>Seq-Scope</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000390</t>
-  </si>
-  <si>
-    <t>CosMx Transcriptomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000218</t>
-  </si>
-  <si>
-    <t>CyCIF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000200</t>
-  </si>
-  <si>
-    <t>Light Sheet</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000168</t>
-  </si>
-  <si>
-    <t>seqFISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000397</t>
-  </si>
-  <si>
-    <t>ATACseq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000309</t>
-  </si>
-  <si>
-    <t>CosMx Proteomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000435</t>
-  </si>
-  <si>
-    <t>Singular Genomics G4X</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000429</t>
-  </si>
-  <si>
-    <t>Visium HD</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000451</t>
-  </si>
-  <si>
-    <t>MERFISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000221</t>
-  </si>
-  <si>
-    <t>10X Multiome</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000215</t>
-  </si>
-  <si>
-    <t>4i</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000447</t>
-  </si>
-  <si>
-    <t>PhenoCycler</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000199</t>
-  </si>
-  <si>
-    <t>Second Harmonic Generation (SHG)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000208</t>
-  </si>
-  <si>
-    <t>Thick section Multiphoton MxIF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000207</t>
-  </si>
-  <si>
-    <t>CyTOF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000407</t>
-  </si>
-  <si>
-    <t>Olink</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000441</t>
-  </si>
-  <si>
-    <t>MIBI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000172</t>
-  </si>
-  <si>
-    <t>Auto-fluorescence</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000205</t>
-  </si>
-  <si>
-    <t>FACS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000440</t>
-  </si>
-  <si>
-    <t>Xenium</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
-  </si>
-  <si>
-    <t>SIMS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000202</t>
-  </si>
-  <si>
-    <t>Cell DIVE</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000159</t>
-  </si>
-  <si>
-    <t>CODEX</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000160</t>
-  </si>
-  <si>
-    <t>GeoMx (NGS)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000300</t>
-  </si>
-  <si>
-    <t>MUSIC</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000328</t>
-  </si>
-  <si>
-    <t>Pixel-seqV2</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000450</t>
-  </si>
-  <si>
-    <t>MALDI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000201</t>
-  </si>
-  <si>
-    <t>2D Imaging Mass Cytometry</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000296</t>
-  </si>
-  <si>
-    <t>Histology</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000197</t>
-  </si>
-  <si>
-    <t>Enhanced Stimulated Raman Spectroscopy (SRS)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
-  </si>
-  <si>
-    <t>DART-FISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000396</t>
-  </si>
-  <si>
-    <t>Resolve</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000384</t>
-  </si>
-  <si>
-    <t>RNAseq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000310</t>
-  </si>
-  <si>
-    <t>LC-MS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000194</t>
-  </si>
-  <si>
-    <t>nanoSPLITS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000312</t>
-  </si>
-  <si>
-    <t>GeoMx (nCounter)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000301</t>
-  </si>
-  <si>
-    <t>RNAseq (with probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
-  </si>
-  <si>
-    <t>MS Lipidomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000405</t>
-  </si>
-  <si>
-    <t>MPLEx</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000448</t>
+    <t>Virtual Histology</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000473</t>
+  </si>
+  <si>
+    <t>Raman Imaging</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000475</t>
+  </si>
+  <si>
+    <t>STARmap</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000476</t>
+  </si>
+  <si>
+    <t>iCLAP</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000479</t>
+  </si>
+  <si>
+    <t>MACSima</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000480</t>
+  </si>
+  <si>
+    <t>Illumina Spatial ver0</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000487</t>
+  </si>
+  <si>
+    <t>DNA Methylation</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000490</t>
+  </si>
+  <si>
+    <t>Paired-Tag</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000492</t>
+  </si>
+  <si>
+    <t>snm3C-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000504</t>
+  </si>
+  <si>
+    <t>Whole Exome Sequencing</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000514</t>
   </si>
   <si>
     <t>contributors_path</t>
@@ -424,7 +484,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2025-10-21T13:32:53-07:00</t>
+    <t>2026-10-21T13:39:14-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -529,27 +589,27 @@
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>106</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2">
       <c r="D2" t="s" s="5">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="G2" t="s" s="8">
-        <v>107</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" sqref="D2:D1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'dataset_type'!$A$1:$A$50</formula1>
+      <formula1>'dataset_type'!$A$1:$A$60</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -560,7 +620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -961,6 +1021,86 @@
       </c>
       <c r="B50" t="s" s="0">
         <v>103</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -981,30 +1121,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>114</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>115</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
